--- a/INFO/M1 测试治具PC端通讯协议.xlsx
+++ b/INFO/M1 测试治具PC端通讯协议.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="120">
   <si>
     <t>单帧数据结构 (最低10字节）</t>
   </si>
@@ -351,6 +351,59 @@
   </si>
   <si>
     <t>状态码：0x00=成功, 0x0C=失败(失败时版本号 00 FF FF)</t>
+  </si>
+  <si>
+    <t>测量ADC</t>
+  </si>
+  <si>
+    <t>0E</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1字节u8：模式</t>
+  </si>
+  <si>
+    <t>00=只读最近一批（不触发测试）　01=触发一次测试</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测量ADC ACK </t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1字节u8：状态码
+55字节：U1测量快照
+21字节：交叉校验块
+</t>
+  </si>
+  <si>
+    <t>快照：flags(1) + 通道数(1) + 回合号(2) + 间隔ms(2) + VDDA(2) + 配置指纹(2) + 9×5B（raw u16／mv u16 输入侧mV／flags u8：（bit0 ok、bit1 贴边））
+顺序 = 24V, 10V, 5V, 3.3V, A相, B相, C相, 电流1, 电流2
+交叉校验快：flags(1)（bit0 做过校验／bit1 有超差／bit2 U2 无应答）+ 超差掩码(2) + U2 的 9×mv u16(18)</t>
+  </si>
+  <si>
+    <t>脉冲捕获（TIM 三相）</t>
+  </si>
+  <si>
+    <t>0F</t>
+  </si>
+  <si>
+    <t>00=只读最近一个窗口　01=触发一次 200ms 捕获</t>
+  </si>
+  <si>
+    <t>脉冲捕获 ACK</t>
+  </si>
+  <si>
+    <t>1字节u8:状态码
+45字节：U1脉冲结果
+45字节：U2脉冲结果</t>
+  </si>
+  <si>
+    <t>U1脉冲结果：ver(1) + flags(1)（bit0 数据有效／bit1 至少一相没信号）+ 窗口ms(2) + 相数=3(1) + rsvd(1) + 3相×13B
+U2脉冲结果：布局完全同上；U2 没应答时整段按"无数据"打包</t>
   </si>
 </sst>
 </file>
@@ -1234,62 +1287,62 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -2884,52 +2937,116 @@
       <c r="J36" s="11"/>
     </row>
     <row r="37" ht="29.25" customHeight="1" spans="2:10">
-      <c r="B37" s="23"/>
-      <c r="C37" s="30"/>
+      <c r="B37" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>75</v>
+      </c>
       <c r="D37" s="15"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" ht="14.25" spans="2:10">
-      <c r="B38" s="23"/>
-      <c r="C38" s="31"/>
+      <c r="E37" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1" spans="2:10">
+      <c r="B38" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D38" s="15"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="11"/>
+      <c r="E38" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J38" s="30" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="39" ht="35.25" customHeight="1" spans="2:10">
-      <c r="B39" s="23"/>
-      <c r="C39" s="32"/>
+      <c r="B39" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>75</v>
+      </c>
       <c r="D39" s="15"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="11"/>
+      <c r="E39" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G39" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="40" ht="27.75" customHeight="1" spans="2:10">
-      <c r="B40" s="33"/>
-      <c r="C40" s="30"/>
+      <c r="B40" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D40" s="15"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="11"/>
+      <c r="E40" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40" s="9">
+        <v>91</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" s="30" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="41" ht="14.25" spans="2:10">
       <c r="B41" s="23"/>
-      <c r="C41" s="34"/>
+      <c r="C41" s="32"/>
       <c r="D41" s="15"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -2940,7 +3057,7 @@
     </row>
     <row r="42" ht="53.25" customHeight="1" spans="2:10">
       <c r="B42" s="11"/>
-      <c r="C42" s="30"/>
+      <c r="C42" s="33"/>
       <c r="D42" s="15"/>
       <c r="E42" s="10"/>
       <c r="F42" s="9"/>
@@ -2950,19 +3067,19 @@
       <c r="J42" s="11"/>
     </row>
     <row r="43" ht="104.25" customHeight="1" spans="2:10">
-      <c r="B43" s="35"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="41"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="40"/>
     </row>
     <row r="44" ht="12.75" spans="2:10">
       <c r="B44" s="24"/>
-      <c r="C44" s="42"/>
+      <c r="C44" s="41"/>
       <c r="D44" s="24"/>
       <c r="E44" s="24"/>
       <c r="F44" s="24"/>
@@ -2972,48 +3089,48 @@
       <c r="J44" s="24"/>
     </row>
     <row r="45" ht="14.25" spans="2:10">
-      <c r="B45" s="35"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="46"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="45"/>
     </row>
     <row r="46" ht="14.25" spans="2:10">
       <c r="B46" s="11"/>
-      <c r="C46" s="47"/>
+      <c r="C46" s="46"/>
       <c r="D46" s="10"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="10"/>
       <c r="H46" s="25"/>
       <c r="I46" s="10"/>
-      <c r="J46" s="48"/>
+      <c r="J46" s="47"/>
     </row>
     <row r="47" ht="22.5" customHeight="1" spans="2:10">
       <c r="B47" s="11"/>
-      <c r="C47" s="30"/>
+      <c r="C47" s="33"/>
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
-      <c r="J47" s="48"/>
+      <c r="J47" s="47"/>
     </row>
     <row r="48" ht="48.75" customHeight="1" spans="2:10">
       <c r="B48" s="11"/>
-      <c r="C48" s="31"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
       <c r="H48" s="25"/>
       <c r="I48" s="10"/>
-      <c r="J48" s="48"/>
+      <c r="J48" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="1">
